--- a/Team-Data/2014-15/12-31-2014-15.xlsx
+++ b/Team-Data/2014-15/12-31-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>4.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE2" t="n">
         <v>4</v>
@@ -751,7 +818,7 @@
         <v>4</v>
       </c>
       <c r="AH2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
         <v>14</v>
@@ -772,13 +839,13 @@
         <v>6</v>
       </c>
       <c r="AO2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
         <v>29</v>
@@ -787,19 +854,19 @@
         <v>12</v>
       </c>
       <c r="AT2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AU2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY2" t="n">
         <v>11</v>
@@ -808,10 +875,10 @@
         <v>3</v>
       </c>
       <c r="BA2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BC2" t="n">
         <v>7</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -843,88 +910,88 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
         <v>18</v>
       </c>
       <c r="G3" t="n">
-        <v>0.379</v>
+        <v>0.357</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
       </c>
       <c r="I3" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="J3" t="n">
-        <v>87.7</v>
+        <v>87.5</v>
       </c>
       <c r="K3" t="n">
         <v>0.46</v>
       </c>
       <c r="L3" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="M3" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.322</v>
+        <v>0.324</v>
       </c>
       <c r="O3" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="P3" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.759</v>
+        <v>0.756</v>
       </c>
       <c r="R3" t="n">
         <v>10.5</v>
       </c>
       <c r="S3" t="n">
-        <v>33.2</v>
+        <v>33</v>
       </c>
       <c r="T3" t="n">
-        <v>43.7</v>
+        <v>43.5</v>
       </c>
       <c r="U3" t="n">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
       <c r="V3" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="W3" t="n">
         <v>8.4</v>
       </c>
       <c r="X3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y3" t="n">
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AB3" t="n">
         <v>103.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.3</v>
+        <v>-1.1</v>
       </c>
       <c r="AD3" t="n">
         <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF3" t="n">
         <v>18</v>
@@ -933,7 +1000,7 @@
         <v>22</v>
       </c>
       <c r="AH3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI3" t="n">
         <v>3</v>
@@ -942,19 +1009,19 @@
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM3" t="n">
         <v>13</v>
       </c>
       <c r="AN3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP3" t="n">
         <v>27</v>
@@ -972,19 +1039,19 @@
         <v>11</v>
       </c>
       <c r="AU3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW3" t="n">
         <v>8</v>
       </c>
       <c r="AX3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AZ3" t="n">
         <v>18</v>
@@ -996,7 +1063,7 @@
         <v>7</v>
       </c>
       <c r="BC3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -1103,13 +1170,13 @@
         <v>-1.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE4" t="n">
         <v>16</v>
       </c>
       <c r="AF4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG4" t="n">
         <v>16</v>
@@ -1118,25 +1185,25 @@
         <v>8</v>
       </c>
       <c r="AI4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AM4" t="n">
         <v>18</v>
       </c>
       <c r="AN4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP4" t="n">
         <v>18</v>
@@ -1154,7 +1221,7 @@
         <v>21</v>
       </c>
       <c r="AU4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV4" t="n">
         <v>13</v>
@@ -1163,7 +1230,7 @@
         <v>19</v>
       </c>
       <c r="AX4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY4" t="n">
         <v>13</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -1207,49 +1274,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" t="n">
-        <v>0.303</v>
+        <v>0.313</v>
       </c>
       <c r="H5" t="n">
         <v>48.9</v>
       </c>
       <c r="I5" t="n">
-        <v>36.3</v>
+        <v>36.5</v>
       </c>
       <c r="J5" t="n">
-        <v>85</v>
+        <v>85.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.427</v>
+        <v>0.428</v>
       </c>
       <c r="L5" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="M5" t="n">
         <v>19.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0.317</v>
+        <v>0.322</v>
       </c>
       <c r="O5" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="P5" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.741</v>
+        <v>0.737</v>
       </c>
       <c r="R5" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S5" t="n">
         <v>32.5</v>
@@ -1258,49 +1325,49 @@
         <v>42.2</v>
       </c>
       <c r="U5" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V5" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="W5" t="n">
         <v>5.7</v>
       </c>
       <c r="X5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y5" t="n">
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>95.3</v>
+        <v>95.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>-5.1</v>
+        <v>-4.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG5" t="n">
         <v>25</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>26</v>
       </c>
       <c r="AH5" t="n">
         <v>3</v>
       </c>
       <c r="AI5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ5" t="n">
         <v>10</v>
@@ -1309,7 +1376,7 @@
         <v>28</v>
       </c>
       <c r="AL5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM5" t="n">
         <v>25</v>
@@ -1321,7 +1388,7 @@
         <v>23</v>
       </c>
       <c r="AP5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ5" t="n">
         <v>21</v>
@@ -1339,28 +1406,28 @@
         <v>23</v>
       </c>
       <c r="AV5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW5" t="n">
         <v>29</v>
       </c>
       <c r="AX5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AY5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ5" t="n">
         <v>2</v>
       </c>
       <c r="BA5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB5" t="n">
         <v>25</v>
       </c>
       <c r="BC5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -1467,25 +1534,25 @@
         <v>4.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE6" t="n">
         <v>7</v>
       </c>
       <c r="AF6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG6" t="n">
         <v>9</v>
       </c>
       <c r="AH6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AI6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AJ6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK6" t="n">
         <v>19</v>
@@ -1497,7 +1564,7 @@
         <v>17</v>
       </c>
       <c r="AN6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1506,13 +1573,13 @@
         <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT6" t="n">
         <v>4</v>
@@ -1539,7 +1606,7 @@
         <v>3</v>
       </c>
       <c r="BB6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC6" t="n">
         <v>8</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -1571,85 +1638,85 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7" t="n">
         <v>18</v>
       </c>
       <c r="F7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.581</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
       </c>
       <c r="I7" t="n">
-        <v>37.1</v>
+        <v>37.4</v>
       </c>
       <c r="J7" t="n">
-        <v>81.2</v>
+        <v>81</v>
       </c>
       <c r="K7" t="n">
-        <v>0.457</v>
+        <v>0.461</v>
       </c>
       <c r="L7" t="n">
         <v>8.1</v>
       </c>
       <c r="M7" t="n">
-        <v>23.3</v>
+        <v>23</v>
       </c>
       <c r="N7" t="n">
-        <v>0.346</v>
+        <v>0.35</v>
       </c>
       <c r="O7" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="P7" t="n">
-        <v>25.1</v>
+        <v>25.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.768</v>
+        <v>0.766</v>
       </c>
       <c r="R7" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S7" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T7" t="n">
-        <v>41.1</v>
+        <v>40.8</v>
       </c>
       <c r="U7" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="V7" t="n">
         <v>13.9</v>
       </c>
       <c r="W7" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y7" t="n">
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>101.5</v>
+        <v>102.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AE7" t="n">
         <v>12</v>
@@ -1658,22 +1725,22 @@
         <v>11</v>
       </c>
       <c r="AG7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK7" t="n">
         <v>12</v>
       </c>
-      <c r="AH7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>16</v>
-      </c>
       <c r="AL7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM7" t="n">
         <v>12</v>
@@ -1682,25 +1749,25 @@
         <v>17</v>
       </c>
       <c r="AO7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS7" t="n">
         <v>26</v>
       </c>
       <c r="AT7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AV7" t="n">
         <v>9</v>
@@ -1712,19 +1779,19 @@
         <v>23</v>
       </c>
       <c r="AY7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ7" t="n">
         <v>1</v>
       </c>
       <c r="BA7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BC7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -1753,25 +1820,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" t="n">
         <v>23</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>0.719</v>
+        <v>0.697</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
       </c>
       <c r="I8" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="J8" t="n">
-        <v>86.2</v>
+        <v>86</v>
       </c>
       <c r="K8" t="n">
         <v>0.478</v>
@@ -1780,31 +1847,31 @@
         <v>9.5</v>
       </c>
       <c r="M8" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="N8" t="n">
         <v>0.355</v>
       </c>
       <c r="O8" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="P8" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.761</v>
+        <v>0.763</v>
       </c>
       <c r="R8" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S8" t="n">
-        <v>31.2</v>
+        <v>30.9</v>
       </c>
       <c r="T8" t="n">
-        <v>42.1</v>
+        <v>41.8</v>
       </c>
       <c r="U8" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="V8" t="n">
         <v>12.3</v>
@@ -1813,7 +1880,7 @@
         <v>8.1</v>
       </c>
       <c r="X8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y8" t="n">
         <v>3.5</v>
@@ -1822,28 +1889,28 @@
         <v>20.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>109.9</v>
+        <v>109.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>4</v>
       </c>
       <c r="AF8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AH8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI8" t="n">
         <v>1</v>
@@ -1864,28 +1931,28 @@
         <v>15</v>
       </c>
       <c r="AO8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS8" t="n">
         <v>21</v>
       </c>
       <c r="AT8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW8" t="n">
         <v>11</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -2013,19 +2080,19 @@
         <v>-3</v>
       </c>
       <c r="AD9" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE9" t="n">
         <v>19</v>
       </c>
       <c r="AF9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AG9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AI9" t="n">
         <v>15</v>
@@ -2046,13 +2113,13 @@
         <v>29</v>
       </c>
       <c r="AO9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP9" t="n">
         <v>6</v>
       </c>
-      <c r="AP9" t="n">
-        <v>5</v>
-      </c>
       <c r="AQ9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AR9" t="n">
         <v>1</v>
@@ -2064,10 +2131,10 @@
         <v>3</v>
       </c>
       <c r="AU9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AV9" t="n">
         <v>18</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>19</v>
       </c>
       <c r="AW9" t="n">
         <v>22</v>
@@ -2076,16 +2143,16 @@
         <v>19</v>
       </c>
       <c r="AY9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ9" t="n">
         <v>30</v>
       </c>
       <c r="BA9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC9" t="n">
         <v>21</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -2195,19 +2262,19 @@
         <v>-4.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE10" t="n">
         <v>27</v>
       </c>
       <c r="AF10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG10" t="n">
         <v>27</v>
       </c>
       <c r="AH10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI10" t="n">
         <v>26</v>
@@ -2219,13 +2286,13 @@
         <v>29</v>
       </c>
       <c r="AL10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM10" t="n">
         <v>10</v>
       </c>
       <c r="AN10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO10" t="n">
         <v>25</v>
@@ -2243,7 +2310,7 @@
         <v>13</v>
       </c>
       <c r="AT10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU10" t="n">
         <v>22</v>
@@ -2255,7 +2322,7 @@
         <v>18</v>
       </c>
       <c r="AX10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AY10" t="n">
         <v>21</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI11" t="n">
         <v>2</v>
@@ -2404,16 +2471,16 @@
         <v>5</v>
       </c>
       <c r="AM11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN11" t="n">
         <v>7</v>
       </c>
       <c r="AO11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ11" t="n">
         <v>6</v>
@@ -2446,7 +2513,7 @@
         <v>11</v>
       </c>
       <c r="BA11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB11" t="n">
         <v>3</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -2496,40 +2563,40 @@
         <v>48.7</v>
       </c>
       <c r="I12" t="n">
-        <v>35.6</v>
+        <v>35.4</v>
       </c>
       <c r="J12" t="n">
-        <v>82.8</v>
+        <v>82.3</v>
       </c>
       <c r="K12" t="n">
         <v>0.43</v>
       </c>
       <c r="L12" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="M12" t="n">
-        <v>34.4</v>
+        <v>34</v>
       </c>
       <c r="N12" t="n">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="O12" t="n">
-        <v>17.7</v>
+        <v>18.5</v>
       </c>
       <c r="P12" t="n">
-        <v>25</v>
+        <v>26.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.708</v>
+        <v>0.707</v>
       </c>
       <c r="R12" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S12" t="n">
         <v>32.2</v>
       </c>
       <c r="T12" t="n">
-        <v>44.3</v>
+        <v>44.5</v>
       </c>
       <c r="U12" t="n">
         <v>20</v>
@@ -2538,22 +2605,22 @@
         <v>17.4</v>
       </c>
       <c r="W12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="X12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.3</v>
+        <v>21.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>100.8</v>
+        <v>101</v>
       </c>
       <c r="AC12" t="n">
         <v>3.5</v>
@@ -2562,13 +2629,13 @@
         <v>26</v>
       </c>
       <c r="AE12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF12" t="n">
         <v>6</v>
       </c>
       <c r="AG12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH12" t="n">
         <v>7</v>
@@ -2589,28 +2656,28 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AP12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
       </c>
       <c r="AR12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT12" t="n">
         <v>9</v>
       </c>
       <c r="AU12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
@@ -2619,16 +2686,16 @@
         <v>3</v>
       </c>
       <c r="AX12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BB12" t="n">
         <v>17</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
         <v>21</v>
       </c>
       <c r="G13" t="n">
-        <v>0.364</v>
+        <v>0.344</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
@@ -2681,67 +2748,67 @@
         <v>36.3</v>
       </c>
       <c r="J13" t="n">
-        <v>84.09999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="K13" t="n">
-        <v>0.432</v>
+        <v>0.431</v>
       </c>
       <c r="L13" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M13" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0.341</v>
+        <v>0.335</v>
       </c>
       <c r="O13" t="n">
-        <v>15.2</v>
+        <v>14.8</v>
       </c>
       <c r="P13" t="n">
-        <v>20.7</v>
+        <v>20.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.735</v>
+        <v>0.729</v>
       </c>
       <c r="R13" t="n">
         <v>11</v>
       </c>
       <c r="S13" t="n">
-        <v>34.1</v>
+        <v>34.3</v>
       </c>
       <c r="T13" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
       <c r="U13" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V13" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W13" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="X13" t="n">
         <v>4.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.90000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>-1.4</v>
+        <v>-1.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE13" t="n">
         <v>22</v>
@@ -2753,10 +2820,10 @@
         <v>23</v>
       </c>
       <c r="AH13" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ13" t="n">
         <v>13</v>
@@ -2765,13 +2832,13 @@
         <v>25</v>
       </c>
       <c r="AL13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM13" t="n">
         <v>19</v>
       </c>
       <c r="AN13" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AO13" t="n">
         <v>28</v>
@@ -2780,16 +2847,16 @@
         <v>26</v>
       </c>
       <c r="AQ13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR13" t="n">
         <v>14</v>
       </c>
       <c r="AS13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AT13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU13" t="n">
         <v>21</v>
@@ -2801,22 +2868,22 @@
         <v>30</v>
       </c>
       <c r="AX13" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AY13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ13" t="n">
         <v>19</v>
       </c>
       <c r="BA13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC13" t="n">
         <v>20</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>26</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>18</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -2845,61 +2912,61 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F14" t="n">
         <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>0.667</v>
+        <v>0.656</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
       </c>
       <c r="I14" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J14" t="n">
         <v>81.7</v>
       </c>
       <c r="K14" t="n">
-        <v>0.471</v>
+        <v>0.472</v>
       </c>
       <c r="L14" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="N14" t="n">
-        <v>0.387</v>
+        <v>0.385</v>
       </c>
       <c r="O14" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="P14" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.753</v>
+        <v>0.757</v>
       </c>
       <c r="R14" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>32.2</v>
+        <v>31.8</v>
       </c>
       <c r="T14" t="n">
-        <v>40.9</v>
+        <v>40.6</v>
       </c>
       <c r="U14" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="V14" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="W14" t="n">
         <v>7.7</v>
@@ -2908,25 +2975,25 @@
         <v>4.9</v>
       </c>
       <c r="Y14" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>105.9</v>
+        <v>106.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF14" t="n">
         <v>10</v>
@@ -2938,16 +3005,16 @@
         <v>27</v>
       </c>
       <c r="AI14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL14" t="n">
         <v>4</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2</v>
       </c>
       <c r="AM14" t="n">
         <v>5</v>
@@ -2956,22 +3023,22 @@
         <v>2</v>
       </c>
       <c r="AO14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP14" t="n">
         <v>10</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR14" t="n">
         <v>27</v>
       </c>
       <c r="AS14" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AT14" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AU14" t="n">
         <v>5</v>
@@ -2983,19 +3050,19 @@
         <v>13</v>
       </c>
       <c r="AX14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA14" t="n">
         <v>6</v>
       </c>
       <c r="BB14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G15" t="n">
-        <v>0.323</v>
+        <v>0.313</v>
       </c>
       <c r="H15" t="n">
         <v>48.5</v>
       </c>
       <c r="I15" t="n">
-        <v>38.5</v>
+        <v>38.2</v>
       </c>
       <c r="J15" t="n">
-        <v>87.3</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.441</v>
+        <v>0.439</v>
       </c>
       <c r="L15" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M15" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
       <c r="N15" t="n">
-        <v>0.366</v>
+        <v>0.365</v>
       </c>
       <c r="O15" t="n">
-        <v>18.5</v>
+        <v>18.9</v>
       </c>
       <c r="P15" t="n">
-        <v>25</v>
+        <v>25.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.741</v>
+        <v>0.743</v>
       </c>
       <c r="R15" t="n">
         <v>12.1</v>
       </c>
       <c r="S15" t="n">
-        <v>30.7</v>
+        <v>30.5</v>
       </c>
       <c r="T15" t="n">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
       <c r="U15" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="V15" t="n">
         <v>12.5</v>
@@ -3087,40 +3154,40 @@
         <v>7.6</v>
       </c>
       <c r="X15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>103</v>
+        <v>102.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.1</v>
+        <v>-6.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="AE15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG15" t="n">
         <v>25</v>
       </c>
       <c r="AH15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI15" t="n">
         <v>12</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>10</v>
       </c>
       <c r="AJ15" t="n">
         <v>2</v>
@@ -3129,7 +3196,7 @@
         <v>23</v>
       </c>
       <c r="AL15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM15" t="n">
         <v>21</v>
@@ -3138,25 +3205,25 @@
         <v>9</v>
       </c>
       <c r="AO15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AP15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV15" t="n">
         <v>6</v>
@@ -3165,7 +3232,7 @@
         <v>14</v>
       </c>
       <c r="AX15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY15" t="n">
         <v>7</v>
@@ -3174,7 +3241,7 @@
         <v>20</v>
       </c>
       <c r="BA15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BB15" t="n">
         <v>8</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>4.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
@@ -3308,7 +3375,7 @@
         <v>14</v>
       </c>
       <c r="AK16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL16" t="n">
         <v>28</v>
@@ -3317,13 +3384,13 @@
         <v>27</v>
       </c>
       <c r="AN16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ16" t="n">
         <v>5</v>
@@ -3341,13 +3408,13 @@
         <v>9</v>
       </c>
       <c r="AV16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW16" t="n">
         <v>10</v>
       </c>
       <c r="AX16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY16" t="n">
         <v>22</v>
@@ -3359,7 +3426,7 @@
         <v>17</v>
       </c>
       <c r="BB16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BC16" t="n">
         <v>6</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -3391,46 +3458,46 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E17" t="n">
         <v>14</v>
       </c>
       <c r="F17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G17" t="n">
-        <v>0.424</v>
+        <v>0.438</v>
       </c>
       <c r="H17" t="n">
         <v>48</v>
       </c>
       <c r="I17" t="n">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="J17" t="n">
-        <v>74.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="K17" t="n">
-        <v>0.464</v>
+        <v>0.463</v>
       </c>
       <c r="L17" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M17" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0.358</v>
+        <v>0.359</v>
       </c>
       <c r="O17" t="n">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="P17" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.734</v>
+        <v>0.733</v>
       </c>
       <c r="R17" t="n">
         <v>8.199999999999999</v>
@@ -3445,19 +3512,19 @@
         <v>19.8</v>
       </c>
       <c r="V17" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W17" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Y17" t="n">
         <v>4.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA17" t="n">
         <v>20.8</v>
@@ -3466,16 +3533,16 @@
         <v>94.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>-3.4</v>
+        <v>-3.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE17" t="n">
         <v>18</v>
       </c>
       <c r="AF17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
         <v>18</v>
@@ -3490,7 +3557,7 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AL17" t="n">
         <v>13</v>
@@ -3499,16 +3566,16 @@
         <v>16</v>
       </c>
       <c r="AN17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3526,7 +3593,7 @@
         <v>12</v>
       </c>
       <c r="AW17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX17" t="n">
         <v>30</v>
@@ -3538,10 +3605,10 @@
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BB17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC17" t="n">
         <v>22</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -3573,94 +3640,94 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F18" t="n">
         <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>0.515</v>
+        <v>0.5</v>
       </c>
       <c r="H18" t="n">
         <v>48.8</v>
       </c>
       <c r="I18" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J18" t="n">
-        <v>81.5</v>
+        <v>81.3</v>
       </c>
       <c r="K18" t="n">
         <v>0.464</v>
       </c>
       <c r="L18" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="M18" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0.364</v>
+        <v>0.361</v>
       </c>
       <c r="O18" t="n">
-        <v>16.7</v>
+        <v>17.1</v>
       </c>
       <c r="P18" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.776</v>
+        <v>0.78</v>
       </c>
       <c r="R18" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="S18" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="T18" t="n">
-        <v>40.9</v>
+        <v>40.5</v>
       </c>
       <c r="U18" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V18" t="n">
-        <v>16.9</v>
+        <v>17.1</v>
       </c>
       <c r="W18" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="X18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y18" t="n">
         <v>4.9</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE18" t="n">
         <v>14</v>
       </c>
       <c r="AF18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH18" t="n">
         <v>5</v>
@@ -3669,40 +3736,40 @@
         <v>13</v>
       </c>
       <c r="AJ18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AK18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AL18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM18" t="n">
         <v>24</v>
       </c>
       <c r="AN18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AO18" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AP18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR18" t="n">
         <v>22</v>
       </c>
       <c r="AS18" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AT18" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AU18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV18" t="n">
         <v>28</v>
@@ -3717,16 +3784,16 @@
         <v>15</v>
       </c>
       <c r="AZ18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA18" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BB18" t="n">
         <v>19</v>
       </c>
       <c r="BC18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -3845,13 +3912,13 @@
         <v>28</v>
       </c>
       <c r="AH19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -3863,16 +3930,16 @@
         <v>30</v>
       </c>
       <c r="AN19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP19" t="n">
         <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR19" t="n">
         <v>3</v>
@@ -3887,7 +3954,7 @@
         <v>12</v>
       </c>
       <c r="AV19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW19" t="n">
         <v>4</v>
@@ -3899,13 +3966,13 @@
         <v>27</v>
       </c>
       <c r="AZ19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA19" t="n">
         <v>4</v>
       </c>
       <c r="BB19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC19" t="n">
         <v>29</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -3940,100 +4007,100 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
+        <v>16</v>
+      </c>
+      <c r="F20" t="n">
         <v>15</v>
       </c>
-      <c r="F20" t="n">
-        <v>16</v>
-      </c>
       <c r="G20" t="n">
-        <v>0.484</v>
+        <v>0.516</v>
       </c>
       <c r="H20" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>38.9</v>
+        <v>39.2</v>
       </c>
       <c r="J20" t="n">
-        <v>84.90000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="K20" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L20" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M20" t="n">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
       <c r="N20" t="n">
         <v>0.338</v>
       </c>
       <c r="O20" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P20" t="n">
-        <v>22.4</v>
+        <v>22.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.765</v>
+        <v>0.75</v>
       </c>
       <c r="R20" t="n">
-        <v>11.3</v>
+        <v>11.8</v>
       </c>
       <c r="S20" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="T20" t="n">
-        <v>42.8</v>
+        <v>43.1</v>
       </c>
       <c r="U20" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V20" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="W20" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X20" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="Y20" t="n">
         <v>5.9</v>
       </c>
       <c r="Z20" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="AB20" t="n">
-        <v>101.6</v>
+        <v>101.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.8</v>
+        <v>-0.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF20" t="n">
         <v>13</v>
       </c>
       <c r="AG20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AI20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>8</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>11</v>
       </c>
       <c r="AK20" t="n">
         <v>14</v>
@@ -4048,49 +4115,49 @@
         <v>23</v>
       </c>
       <c r="AO20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP20" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AR20" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AS20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU20" t="n">
         <v>14</v>
       </c>
       <c r="AV20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY20" t="n">
         <v>29</v>
       </c>
       <c r="AZ20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -4119,52 +4186,52 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E21" t="n">
         <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G21" t="n">
-        <v>0.147</v>
+        <v>0.152</v>
       </c>
       <c r="H21" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J21" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="K21" t="n">
-        <v>0.446</v>
+        <v>0.448</v>
       </c>
       <c r="L21" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M21" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="N21" t="n">
-        <v>0.35</v>
+        <v>0.353</v>
       </c>
       <c r="O21" t="n">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="P21" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.79</v>
+        <v>0.793</v>
       </c>
       <c r="R21" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S21" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="T21" t="n">
         <v>39.4</v>
@@ -4173,31 +4240,31 @@
         <v>21.2</v>
       </c>
       <c r="V21" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="W21" t="n">
         <v>7.1</v>
       </c>
       <c r="X21" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y21" t="n">
         <v>3.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>94.09999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>-7.2</v>
+        <v>-6.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="n">
         <v>28</v>
@@ -4209,19 +4276,19 @@
         <v>29</v>
       </c>
       <c r="AH21" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AI21" t="n">
         <v>21</v>
       </c>
       <c r="AJ21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM21" t="n">
         <v>22</v>
@@ -4239,7 +4306,7 @@
         <v>2</v>
       </c>
       <c r="AR21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS21" t="n">
         <v>29</v>
@@ -4251,7 +4318,7 @@
         <v>15</v>
       </c>
       <c r="AV21" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AW21" t="n">
         <v>21</v>
@@ -4269,7 +4336,7 @@
         <v>26</v>
       </c>
       <c r="BB21" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BC21" t="n">
         <v>28</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -4301,97 +4368,97 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
         <v>17</v>
       </c>
       <c r="G22" t="n">
-        <v>0.485</v>
+        <v>0.469</v>
       </c>
       <c r="H22" t="n">
-        <v>48.5</v>
+        <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J22" t="n">
-        <v>83.3</v>
+        <v>82.8</v>
       </c>
       <c r="K22" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L22" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="M22" t="n">
-        <v>22.1</v>
+        <v>21.7</v>
       </c>
       <c r="N22" t="n">
         <v>0.324</v>
       </c>
       <c r="O22" t="n">
-        <v>18.1</v>
+        <v>17.3</v>
       </c>
       <c r="P22" t="n">
-        <v>24.3</v>
+        <v>23.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.745</v>
+        <v>0.735</v>
       </c>
       <c r="R22" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="S22" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="T22" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
       <c r="U22" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="V22" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W22" t="n">
         <v>6.7</v>
       </c>
       <c r="X22" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y22" t="n">
         <v>4.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.8</v>
+        <v>20.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>99.2</v>
+        <v>98</v>
       </c>
       <c r="AC22" t="n">
         <v>1.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF22" t="n">
         <v>17</v>
       </c>
       <c r="AG22" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AH22" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AI22" t="n">
         <v>18</v>
@@ -4403,28 +4470,28 @@
         <v>22</v>
       </c>
       <c r="AL22" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AM22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP22" t="n">
         <v>14</v>
       </c>
-      <c r="AN22" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>12</v>
-      </c>
       <c r="AQ22" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AR22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS22" t="n">
         <v>4</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>5</v>
       </c>
       <c r="AT22" t="n">
         <v>2</v>
@@ -4436,25 +4503,25 @@
         <v>25</v>
       </c>
       <c r="AW22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
         <v>14</v>
       </c>
       <c r="AZ22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA22" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="BB22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -4483,55 +4550,55 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E23" t="n">
         <v>13</v>
       </c>
       <c r="F23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G23" t="n">
-        <v>0.382</v>
+        <v>0.371</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>36.9</v>
+        <v>36.7</v>
       </c>
       <c r="J23" t="n">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
       <c r="K23" t="n">
-        <v>0.46</v>
+        <v>0.457</v>
       </c>
       <c r="L23" t="n">
         <v>7.1</v>
       </c>
       <c r="M23" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="N23" t="n">
         <v>0.374</v>
       </c>
       <c r="O23" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="P23" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.719</v>
+        <v>0.72</v>
       </c>
       <c r="R23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>31.9</v>
+        <v>32.1</v>
       </c>
       <c r="T23" t="n">
-        <v>40.4</v>
+        <v>40.9</v>
       </c>
       <c r="U23" t="n">
         <v>19.9</v>
@@ -4543,22 +4610,22 @@
         <v>6.7</v>
       </c>
       <c r="X23" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA23" t="n">
         <v>18.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.2</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.1</v>
+        <v>-5.4</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4567,7 +4634,7 @@
         <v>19</v>
       </c>
       <c r="AF23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG23" t="n">
         <v>21</v>
@@ -4576,22 +4643,22 @@
         <v>28</v>
       </c>
       <c r="AI23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ23" t="n">
         <v>27</v>
       </c>
       <c r="AK23" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AL23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM23" t="n">
         <v>26</v>
       </c>
       <c r="AN23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO23" t="n">
         <v>30</v>
@@ -4600,31 +4667,31 @@
         <v>29</v>
       </c>
       <c r="AQ23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR23" t="n">
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AT23" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AU23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX23" t="n">
         <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
         <v>17</v>
@@ -4633,10 +4700,10 @@
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -4755,19 +4822,19 @@
         <v>30</v>
       </c>
       <c r="AH24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
       </c>
       <c r="AJ24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK24" t="n">
         <v>30</v>
       </c>
       <c r="AL24" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AM24" t="n">
         <v>11</v>
@@ -4776,22 +4843,22 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP24" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS24" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AT24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU24" t="n">
         <v>28</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -4847,58 +4914,58 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E25" t="n">
         <v>18</v>
       </c>
       <c r="F25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G25" t="n">
-        <v>0.529</v>
+        <v>0.545</v>
       </c>
       <c r="H25" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I25" t="n">
-        <v>39.5</v>
+        <v>39.3</v>
       </c>
       <c r="J25" t="n">
-        <v>85.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L25" t="n">
         <v>10.1</v>
       </c>
       <c r="M25" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="N25" t="n">
-        <v>0.374</v>
+        <v>0.371</v>
       </c>
       <c r="O25" t="n">
-        <v>17.4</v>
+        <v>17.1</v>
       </c>
       <c r="P25" t="n">
-        <v>21.7</v>
+        <v>21.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.801</v>
+        <v>0.8</v>
       </c>
       <c r="R25" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S25" t="n">
         <v>31.4</v>
       </c>
       <c r="T25" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U25" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V25" t="n">
         <v>14.8</v>
@@ -4907,25 +4974,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y25" t="n">
         <v>3.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>22.7</v>
+        <v>22.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="AB25" t="n">
-        <v>106.5</v>
+        <v>105.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
         <v>12</v>
@@ -4937,16 +5004,16 @@
         <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AI25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ25" t="n">
         <v>6</v>
       </c>
       <c r="AK25" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AL25" t="n">
         <v>3</v>
@@ -4955,49 +5022,49 @@
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AO25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AQ25" t="n">
         <v>1</v>
       </c>
       <c r="AR25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS25" t="n">
         <v>19</v>
       </c>
-      <c r="AS25" t="n">
+      <c r="AT25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AV25" t="n">
         <v>20</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>18</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>21</v>
       </c>
       <c r="AW25" t="n">
         <v>9</v>
       </c>
       <c r="AX25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY25" t="n">
         <v>6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BA25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC25" t="n">
         <v>14</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>7.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -5119,7 +5186,7 @@
         <v>2</v>
       </c>
       <c r="AH26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI26" t="n">
         <v>6</v>
@@ -5131,16 +5198,16 @@
         <v>18</v>
       </c>
       <c r="AL26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AM26" t="n">
         <v>3</v>
       </c>
       <c r="AN26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP26" t="n">
         <v>28</v>
@@ -5149,7 +5216,7 @@
         <v>3</v>
       </c>
       <c r="AR26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS26" t="n">
         <v>1</v>
@@ -5164,7 +5231,7 @@
         <v>10</v>
       </c>
       <c r="AW26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX26" t="n">
         <v>7</v>
@@ -5173,7 +5240,7 @@
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA26" t="n">
         <v>25</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -5211,46 +5278,46 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E27" t="n">
         <v>13</v>
       </c>
       <c r="F27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G27" t="n">
-        <v>0.406</v>
+        <v>0.419</v>
       </c>
       <c r="H27" t="n">
         <v>48.8</v>
       </c>
       <c r="I27" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J27" t="n">
-        <v>79.59999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.458</v>
+        <v>0.461</v>
       </c>
       <c r="L27" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="M27" t="n">
         <v>15.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0.341</v>
+        <v>0.347</v>
       </c>
       <c r="O27" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="P27" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.772</v>
+        <v>0.775</v>
       </c>
       <c r="R27" t="n">
         <v>11.3</v>
@@ -5259,43 +5326,43 @@
         <v>33.4</v>
       </c>
       <c r="T27" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="U27" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="V27" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="W27" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="X27" t="n">
         <v>3.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>101.9</v>
+        <v>102.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.1</v>
+        <v>-1.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AE27" t="n">
         <v>19</v>
       </c>
       <c r="AF27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG27" t="n">
         <v>19</v>
@@ -5310,7 +5377,7 @@
         <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AL27" t="n">
         <v>29</v>
@@ -5319,7 +5386,7 @@
         <v>29</v>
       </c>
       <c r="AN27" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5328,7 +5395,7 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR27" t="n">
         <v>13</v>
@@ -5340,13 +5407,13 @@
         <v>8</v>
       </c>
       <c r="AU27" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AV27" t="n">
         <v>27</v>
       </c>
       <c r="AW27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX27" t="n">
         <v>28</v>
@@ -5355,16 +5422,16 @@
         <v>30</v>
       </c>
       <c r="AZ27" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BA27" t="n">
         <v>1</v>
       </c>
       <c r="BB27" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BC27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -5405,25 +5472,25 @@
         <v>0.576</v>
       </c>
       <c r="H28" t="n">
-        <v>49.4</v>
+        <v>49.2</v>
       </c>
       <c r="I28" t="n">
         <v>38.4</v>
       </c>
       <c r="J28" t="n">
-        <v>82.90000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="K28" t="n">
-        <v>0.464</v>
+        <v>0.466</v>
       </c>
       <c r="L28" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="N28" t="n">
-        <v>0.368</v>
+        <v>0.377</v>
       </c>
       <c r="O28" t="n">
         <v>17.3</v>
@@ -5432,31 +5499,31 @@
         <v>22.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.763</v>
+        <v>0.768</v>
       </c>
       <c r="R28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="S28" t="n">
-        <v>34.5</v>
+        <v>34.1</v>
       </c>
       <c r="T28" t="n">
-        <v>44.3</v>
+        <v>44</v>
       </c>
       <c r="U28" t="n">
         <v>24.2</v>
       </c>
       <c r="V28" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="W28" t="n">
         <v>7.5</v>
       </c>
       <c r="X28" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z28" t="n">
         <v>19.6</v>
@@ -5465,58 +5532,58 @@
         <v>20.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>102.2</v>
+        <v>102.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
         <v>11</v>
       </c>
       <c r="AF28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH28" t="n">
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ28" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AL28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ28" t="n">
         <v>11</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>15</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>17</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>13</v>
       </c>
       <c r="AR28" t="n">
         <v>25</v>
       </c>
       <c r="AS28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AT28" t="n">
         <v>10</v>
@@ -5525,25 +5592,25 @@
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW28" t="n">
         <v>15</v>
       </c>
       <c r="AX28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY28" t="n">
         <v>10</v>
       </c>
       <c r="AZ28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC28" t="n">
         <v>9</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>8</v>
       </c>
       <c r="AD29" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
         <v>3</v>
@@ -5668,10 +5735,10 @@
         <v>9</v>
       </c>
       <c r="AI29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK29" t="n">
         <v>10</v>
@@ -5683,19 +5750,19 @@
         <v>8</v>
       </c>
       <c r="AN29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO29" t="n">
         <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ29" t="n">
         <v>4</v>
       </c>
       <c r="AR29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS29" t="n">
         <v>27</v>
@@ -5707,10 +5774,10 @@
         <v>17</v>
       </c>
       <c r="AV29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX29" t="n">
         <v>22</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -5835,16 +5902,16 @@
         <v>-3.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF30" t="n">
         <v>22</v>
       </c>
       <c r="AG30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH30" t="n">
         <v>29</v>
@@ -5868,31 +5935,31 @@
         <v>25</v>
       </c>
       <c r="AO30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ30" t="n">
         <v>18</v>
       </c>
       <c r="AR30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS30" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AT30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU30" t="n">
         <v>24</v>
       </c>
       <c r="AV30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX30" t="n">
         <v>8</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>2.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE31" t="n">
         <v>7</v>
@@ -6026,22 +6093,22 @@
         <v>6</v>
       </c>
       <c r="AG31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM31" t="n">
         <v>28</v>
@@ -6056,7 +6123,7 @@
         <v>22</v>
       </c>
       <c r="AQ31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR31" t="n">
         <v>18</v>
@@ -6071,7 +6138,7 @@
         <v>4</v>
       </c>
       <c r="AV31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW31" t="n">
         <v>12</v>
@@ -6086,7 +6153,7 @@
         <v>23</v>
       </c>
       <c r="BA31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB31" t="n">
         <v>18</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-31-2014-15</t>
+          <t>2014-12-31</t>
         </is>
       </c>
     </row>
